--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -618,10 +618,14 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>EVENT</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+          <t>CRON</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>*/5 * * * *</t>
+        </is>
+      </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
           <t>default-calendar</t>
@@ -884,7 +888,7 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>EVENT</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
@@ -1033,17 +1037,17 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>https://risk-engine.tc.example.com/ingest</t>
+          <t>http://mockserver:1080/tc/ingest</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>OAUTH2</t>
+          <t>TOKEN</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>{"url":"https://risk-engine.tc.example.com/ingest","clientId":"tc-batch","tokenEndpoint":"https://auth.tc.example.com/token"}</t>
+          <t>{"url":"http://mockserver:1080/tc/ingest","method":"POST","tokenHeader":"X-API-Token"}</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -1083,17 +1087,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>sftp-tc.example.com:22</t>
+          <t>sftp:22</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>KEY_PAIR</t>
+          <t>PASSWORD</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>{"host":"sftp-tc.example.com","port":22,"remotePath":"/inbound/risk"}</t>
+          <t>{"host":"sftp","port":22,"username":"tc","password":"tc_pass_123","remotePath":"/inbound"}</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">

--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -933,6 +933,162 @@
       <c r="T5" s="3" t="inlineStr">
         <is>
           <t>事件触发完整风控流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GATEWAY ALL join 工作流</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>WORKFLOW</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>default-calendar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>always-open</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>14400</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>GATEWAY joinMode=ALL 覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GATEWAY N_OF join 工作流</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>WORKFLOW</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>default-calendar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>always-open</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>14400</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>GATEWAY joinMode=N_OF + joinThreshold=2 覆盖</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1850,6 +2006,76 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>风控 GATEWAY ALL 工作流</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DAG</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FORK→3 branch→MERGE(ALL)→END</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>风控 GATEWAY N_OF 工作流</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DAG</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FORK→3 branch→MERGE(N_OF=2)→END + FAILURE / CONDITION 边</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1861,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2166,6 +2392,851 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>{"entry": true}</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>GATEWAY</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Branch A</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TC_IMPORT_RISK_SCORE</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>{"branch": "A"}</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Branch B</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TC_EXPORT_RISK_ALERT</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>{"branch": "B"}</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Branch C</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TC_DISPATCH_REVIEW</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>{"branch": "C"}</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Merge ALL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GATEWAY</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>{"joinMode": "ALL"}</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>{"entry": false}</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>{"entry": true}</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>GATEWAY</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Branch A</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>TC_IMPORT_RISK_SCORE</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>{"branch": "A"}</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Branch B</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>TC_EXPORT_RISK_ALERT</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>{"branch": "B"}</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Branch C</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>TC_DISPATCH_REVIEW</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>{"branch": "C"}</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Merge N_OF</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>GATEWAY</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>{"joinMode": "N_OF", "joinThreshold": 2}</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>{"entry": false}</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FALLBACK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>TC_DISPATCH_REVIEW</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>{"branch": "fallback"}</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2177,7 +3248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2304,6 +3375,641 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CONDITION</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>${bizDate != null}</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>FALLBACK</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FAILURE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FALLBACK</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="job_definition" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="file_channel_config" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="alert_routing_config" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="pipeline_definition" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="pipeline_step_definition" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="workflow_definition" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="workflow_node" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="workflow_edge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="job_definition" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_channel_config" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_template_config" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_definition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_step_definition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_definition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_node" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_edge" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1281,25 +1281,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:AO7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="28" customWidth="1" min="22" max="22"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="34" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="23" customWidth="1" min="34" max="34"/>
+    <col width="30" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="34" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tenant_id</t>
@@ -1307,184 +1335,1230 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>route_code</t>
+          <t>template_code</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>route_name</t>
+          <t>template_name</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>template_type</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>alert_group</t>
+          <t>biz_type</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>file_format_type</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>receiver</t>
+          <t>charset</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>group_by</t>
+          <t>target_charset</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>group_wait_seconds</t>
+          <t>with_bom</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>group_interval_seconds</t>
+          <t>line_separator</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>repeat_interval_seconds</t>
+          <t>delimiter</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>quote_char</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>escape_char</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>record_length</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>header_rows</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>footer_rows</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>header_template</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>trailer_template</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>checksum_type</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>compress_type</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>encrypt_type</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>naming_rule</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>field_mappings</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>validation_rule_set</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>default_query_code</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>default_query_sql</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>query_param_schema</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>streaming_enabled</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>page_size</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>fetch_size</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>chunk_size</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>preview_masking_enabled</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>error_line_masking_enabled</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>log_masking_enabled</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>content_encryption_enabled</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>encryption_key_ref</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>download_requires_approval</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>masking_rule_set</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>TC_RT_RISK_CRITICAL</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>高风险告警</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>risk-oncall</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>risk</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>pagerduty-risk</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>job_code</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>高风险事件立即通知</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TC_IMPORT_RISK_SCORE_TPL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>风险评分导入文件模板</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>IMPORT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DELIMITED</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>\n</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>"</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>\</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>tc_import_risk_score_${batchDate}.csv</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>[{"source":"id","target":"ID"}]</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{"field":"id","rule":"required"}]</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>TC_IMPORT_RISK_SCORE IMPORT 测试文件模板</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>TC_RT_SCORE_WARN</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>评分异常预警</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>risk-ops</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>slack-risk</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>tenant_id</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>900</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>评分数据异常通知</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TC_EXPORT_RISK_ALERT_TPL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>风险预警导出文件模板</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EXPORT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DELIMITED</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>\n</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>"</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>\</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>tc_export_risk_alert_${batchDate}.csv</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>[{"source":"id","target":"ID"}]</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>QRY_TC_EXPORT_RISK_ALERT</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>select * from risk_export</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>TC_EXPORT_RISK_ALERT EXPORT 测试文件模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TC_DISPATCH_REVIEW_TPL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>人工审核分发文件模板</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SHARED</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>tc_dispatch_review_${batchDate}.json</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>[{"source":"id","target":"ID"}]</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>TC_DISPATCH_REVIEW SHARED 测试文件模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE_TPL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>风控流程工作流文件模板</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SHARED</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DELIMITED</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>\n</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>"</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>\</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>tc_wf_risk_pipeline_${batchDate}.csv</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>[{"source":"id","target":"ID"}]</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE SHARED 测试文件模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL_TPL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GATEWAY ALL join 工作流文件模板</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SHARED</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DELIMITED</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>\n</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>"</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>\</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>tc_wf_gateway_all_${batchDate}.csv</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>[{"source":"id","target":"ID"}]</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL SHARED 测试文件模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF_TPL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GATEWAY N_OF join 工作流文件模板</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SHARED</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DELIMITED</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>UTF-8</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>\n</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>"</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>\</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>tc_wf_gateway_n_of_${batchDate}.csv</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>[{"source":"id","target":"ID"}]</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF SHARED 测试文件模板</t>
         </is>
       </c>
     </row>

--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -7,14 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="job_definition" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_channel_config" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_template_config" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_definition" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_step_definition" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_definition" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_node" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_edge" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resource_queue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="business_calendar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="batch_window" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="job_definition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_channel_config" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_template_config" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_definition" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_step_definition" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_definition" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_node" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_edge" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,6 +456,2482 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tenant_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>queue_code</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>queue_name</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>queue_type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>max_running_jobs</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>max_running_partitions</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>max_qps</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>worker_group</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>resource_tag</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>priority_policy</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>fair_share_weight</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>tc-import-queue</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>tc-import-queue资源队列</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>IMPORT</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>tc-import-queue 测试资源队列</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tc-export-queue</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>tc-export-queue资源队列</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EXPORT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>export</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>tc-export-queue 测试资源队列</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tc-dispatch-queue</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>tc-dispatch-queue资源队列</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DISPATCH</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>dispatch</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>tc-dispatch-queue 测试资源队列</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tenant_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>workflow_code</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>workflow_version</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>node_code</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>node_name</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>node_type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>related_job_code</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>related_pipeline_code</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>worker_group</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>window_code</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>node_order</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>retry_policy</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>retry_max_count</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>timeout_seconds</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>node_params</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>NODE_IMPORT</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>导入评分</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>TC_IMPORT_RISK_SCORE</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>always-open</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>EXPONENTIAL</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>NODE_EXPORT</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>推送预警</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>TC_EXPORT_RISK_ALERT</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>export</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>NODE_DISPATCH</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>分发审核</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>TC_DISPATCH_REVIEW</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>dispatch</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>{"entry": true}</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>GATEWAY</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Branch A</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TC_IMPORT_RISK_SCORE</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>{"branch": "A"}</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Branch B</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TC_EXPORT_RISK_ALERT</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>{"branch": "B"}</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Branch C</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TC_DISPATCH_REVIEW</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>{"branch": "C"}</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Merge ALL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GATEWAY</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>{"joinMode": "ALL"}</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>{"entry": false}</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>{"entry": true}</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>GATEWAY</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Branch A</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>TC_IMPORT_RISK_SCORE</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>{"branch": "A"}</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Branch B</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>TC_EXPORT_RISK_ALERT</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>{"branch": "B"}</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Branch C</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>TC_DISPATCH_REVIEW</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>{"branch": "C"}</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Merge N_OF</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>GATEWAY</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>{"joinMode": "N_OF", "joinThreshold": 2}</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>{"entry": false}</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FALLBACK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JOB</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>TC_DISPATCH_REVIEW</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>{"branch": "fallback"}</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tenant_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>workflow_code</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>workflow_version</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>from_node_code</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>to_node_code</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>edge_type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>condition_expr</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>NODE_IMPORT</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>NODE_EXPORT</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>NODE_EXPORT</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>NODE_DISPATCH</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_ALL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CONDITION</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>${bizDate != null}</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BRANCH_C</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>FALLBACK</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FAILURE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FALLBACK</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TC_WF_GATEWAY_N_OF</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ALWAYS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tenant_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>calendar_code</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>calendar_name</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>timezone</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>holiday_roll_rule</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>catch_up_policy</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>catch_up_max_days</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>holidays</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>default-calendar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>default-calendar业务日历</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-01-01,2026-10-01</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>default-calendar 测试业务日历</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tenant_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>window_code</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>window_name</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>timezone</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>start_time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>end_time</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>end_strategy</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>out_of_window_action</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>allow_cross_day</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>always-open</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>always-open批次窗口</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>23:59</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FINISH_RUNNING</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>always-open 测试批次窗口</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1097,7 +3576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1275,7 +3754,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2567,7 +5046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2684,7 +5163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2990,7 +5469,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3153,1938 +5632,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>tenant_id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>workflow_code</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>workflow_version</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>node_code</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>node_name</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>node_type</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>related_job_code</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>related_pipeline_code</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>worker_group</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>window_code</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>node_order</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>retry_policy</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>retry_max_count</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>timeout_seconds</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>node_params</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>TC_WF_RISK_PIPELINE</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>NODE_IMPORT</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>导入评分</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>TC_IMPORT_RISK_SCORE</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>import</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>always-open</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>EXPONENTIAL</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>1800</v>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>TC_WF_RISK_PIPELINE</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>NODE_EXPORT</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>推送预警</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>TC_EXPORT_RISK_ALERT</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>export</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TC_WF_RISK_PIPELINE</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>NODE_DISPATCH</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>分发审核</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>TC_DISPATCH_REVIEW</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>dispatch</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>{"entry": true}</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>FORK</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Fork</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>GATEWAY</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>BRANCH_A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Branch A</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TC_IMPORT_RISK_SCORE</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>{"branch": "A"}</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BRANCH_B</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Branch B</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>TC_EXPORT_RISK_ALERT</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>{"branch": "B"}</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>BRANCH_C</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Branch C</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>TC_DISPATCH_REVIEW</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>{"branch": "C"}</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Merge ALL</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>GATEWAY</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>{"joinMode": "ALL"}</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>{"entry": false}</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>{"entry": true}</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>FORK</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Fork</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>GATEWAY</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>BRANCH_A</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Branch A</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>TC_IMPORT_RISK_SCORE</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>{"branch": "A"}</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>BRANCH_B</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Branch B</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>TC_EXPORT_RISK_ALERT</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>{"branch": "B"}</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>BRANCH_C</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Branch C</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>TC_DISPATCH_REVIEW</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>{"branch": "C"}</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Merge N_OF</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>GATEWAY</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>5</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>{"joinMode": "N_OF", "joinThreshold": 2}</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>6</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>{"entry": false}</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fallback</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>JOB</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>TC_DISPATCH_REVIEW</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>7</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>{"branch": "fallback"}</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>tenant_id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>workflow_code</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>workflow_version</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>from_node_code</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>to_node_code</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>edge_type</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>condition_expr</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>TC_WF_RISK_PIPELINE</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>NODE_IMPORT</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>NODE_EXPORT</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>TC_WF_RISK_PIPELINE</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>NODE_EXPORT</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>NODE_DISPATCH</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>ALWAYS</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FORK</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ALWAYS</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>FORK</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>BRANCH_A</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ALWAYS</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>FORK</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>BRANCH_B</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ALWAYS</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>FORK</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>BRANCH_C</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ALWAYS</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BRANCH_A</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>BRANCH_B</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>BRANCH_C</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_ALL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ALWAYS</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>FORK</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ALWAYS</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>FORK</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>BRANCH_A</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ALWAYS</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>FORK</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>BRANCH_B</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CONDITION</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>${bizDate != null}</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>FORK</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>BRANCH_C</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ALWAYS</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>BRANCH_A</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>BRANCH_B</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>BRANCH_C</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>BRANCH_C</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>FAILURE</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>FALLBACK</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ALWAYS</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>TC_WF_GATEWAY_N_OF</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ALWAYS</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resource_queue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="business_calendar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="batch_window" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="job_definition" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_channel_config" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_template_config" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_definition" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_step_definition" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_definition" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_node" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_edge" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="resource_queue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="business_calendar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="batch_window" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="job_definition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="file_channel_config" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="file_template_config" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="pipeline_definition" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="pipeline_step_definition" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="workflow_definition" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="workflow_node" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="workflow_edge" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>sftpReceiveStep</t>
+          <t>IMPORT_RECEIVE</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>decryptPreprocessStep</t>
+          <t>IMPORT_PREPROCESS</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>jsonParseStep</t>
+          <t>IMPORT_PARSE</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>riskScoreLoadStep</t>
+          <t>IMPORT_LOAD</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">

--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -729,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1879,6 +1879,114 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>开始</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>结束</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1890,7 +1998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2647,6 +2755,76 @@
         </is>
       </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NODE_IMPORT</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NODE_DISPATCH</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -3102,7 +3280,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>*/5 * * * *</t>
+          <t>0 */5 * * * ?</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -3200,7 +3378,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>*/30 * * * *</t>
+          <t>0 */30 * * * ?</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
@@ -3732,7 +3910,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>{"host":"sftp","port":22,"username":"tc","password":"tc_pass_123","remotePath":"/inbound"}</t>
+          <t>{"sftp_host": "sftp", "sftp_port": 22, "sftp_username": "tc", "sftp_password": "tc_pass_123", "sftp_remote_path": "/inbound"}</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">

--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -3110,7 +3110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3236,6 +3236,11 @@
           <t>description</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>execution_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -3334,6 +3339,11 @@
           <t>事件驱动风险评分导入</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3426,6 +3436,11 @@
       <c r="T3" s="3" t="inlineStr">
         <is>
           <t>每30分钟推送风险预警</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>FULL</t>
         </is>
       </c>
     </row>
@@ -3514,6 +3529,11 @@
           <t>触发人工审核任务分发</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3592,6 +3612,11 @@
           <t>事件触发完整风控流程</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3670,6 +3695,11 @@
           <t>GATEWAY joinMode=ALL 覆盖</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3746,6 +3776,11 @@
       <c r="T7" t="inlineStr">
         <is>
           <t>GATEWAY joinMode=N_OF + joinThreshold=2 覆盖</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>FULL</t>
         </is>
       </c>
     </row>

--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -3110,7 +3110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3239,6 +3239,11 @@
       <c r="U1" t="inlineStr">
         <is>
           <t>execution_mode</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>watermark_field</t>
         </is>
       </c>
     </row>

--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -4338,7 +4338,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[{"source":"id","target":"ID"}]</t>
+          <t>[{"name":"entity_id","targetColumn":"entity_id","type":"STRING","required":true},{"name":"entity_type","targetColumn":"entity_type","type":"STRING","required":true},{"name":"score_value","targetColumn":"score_value","type":"INTEGER","required":true},{"name":"score_band","targetColumn":"score_band","type":"STRING","required":true},{"name":"score_date","targetColumn":"score_date","type":"DATE","required":true,"format":"yyyy-MM-dd"}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[{"source":"id","target":"ID"}]</t>
+          <t>[{"name":"id","sourceColumn":"id","header":"ID"},{"name":"tenant_id","sourceColumn":"tenant_id","header":"Tenant"},{"name":"entity_id","sourceColumn":"entity_id","header":"Entity ID"},{"name":"entity_type","sourceColumn":"entity_type","header":"Entity Type"},{"name":"score_value","sourceColumn":"score_value","header":"Score"},{"name":"score_band","sourceColumn":"score_band","header":"Band"},{"name":"score_date","sourceColumn":"score_date","header":"Score Date","type":"DATE","format":"yyyy-MM-dd"}]</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>select * from risk_export</t>
+          <t>SELECT id, tenant_id, entity_id, entity_type, score_value, score_band, score_date FROM biz.risk_score WHERE tenant_id = :tenantId AND (:batchNo IS NULL OR :batchNo IS NOT NULL)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[{"source":"id","target":"ID"}]</t>
+          <t>[{"source":"id","target":"ID","name":"id"}]</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[{"source":"id","target":"ID"}]</t>
+          <t>[{"source":"id","target":"ID","name":"id"}]</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[{"source":"id","target":"ID"}]</t>
+          <t>[{"source":"id","target":"ID","name":"id"}]</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[{"source":"id","target":"ID"}]</t>
+          <t>[{"source":"id","target":"ID","name":"id"}]</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">

--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -4343,7 +4343,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[{"field":"id","rule":"required"}]</t>
+          <t>{"fieldRules":{"entity_id":{"required":true,"errorCode":"IMPORT_VALIDATE_REQUIRED"},"entity_type":{"required":true,"errorCode":"IMPORT_VALIDATE_REQUIRED"},"score_value":{"required":true,"errorCode":"IMPORT_VALIDATE_REQUIRED"},"score_band":{"required":true,"errorCode":"IMPORT_VALIDATE_REQUIRED"},"score_date":{"required":true,"errorCode":"IMPORT_VALIDATE_REQUIRED"}}}</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>SELECT id, tenant_id, entity_id, entity_type, score_value, score_band, score_date FROM biz.risk_score WHERE tenant_id = :tenantId AND (:batchNo IS NULL OR :batchNo IS NOT NULL)</t>
+          <t>SELECT id, tenant_id, entity_id, entity_type, score_value, score_band, score_date FROM biz.risk_score WHERE tenant_id = :tenantId AND CAST(:batchNo AS text) IS NOT NULL</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">

--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -3110,7 +3110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3136,490 +3136,486 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tenant_id</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>job_code</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>job_name</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>job_type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>biz_type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>queue_code</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>worker_group</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>schedule_type</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>schedule_expr</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>depends_on_job_code</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>calendar_code</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>window_code</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>retry_policy</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>retry_max_count</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>timeout_seconds</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>shard_strategy</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>execution_mode</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>watermark_field</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>execution_handler</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>param_schema</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>default_params</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>execution_mode</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>watermark_field</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>TC_IMPORT_RISK_SCORE</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>风险评分导入</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>IMPORT</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>tc-import-queue</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>import</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>CRON</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0 */5 * * * ?</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>default-calendar</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>always-open</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>EXPONENTIAL</t>
         </is>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="O2" t="n">
         <v>1800</v>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>riskScoreImportHandler</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>事件驱动风险评分导入</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TC_EXPORT_RISK_ALERT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>风险预警导出</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EXPORT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>tc-export-queue</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>export</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CRON</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0 */30 * * * ?</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>always-open</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>600</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>FULL</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>TC_EXPORT_RISK_ALERT</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>风险预警导出</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>EXPORT</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>riskAlertExportHandler</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>每30分钟推送风险预警</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TC_DISPATCH_REVIEW</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>人工审核分发</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DISPATCH</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>tc-dispatch-queue</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>dispatch</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>300</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>reviewDispatchHandler</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>触发人工审核任务分发</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TC_WF_RISK_PIPELINE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>风控流程工作流</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>WORKFLOW</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>RISK</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>tc-export-queue</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>export</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>CRON</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>0 */30 * * * ?</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>always-open</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>default-calendar</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>riskAlertExportHandler</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3600</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>每30分钟推送风险预警</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TC_DISPATCH_REVIEW</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>人工审核分发</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>DISPATCH</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>tc-dispatch-queue</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>dispatch</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>reviewDispatchHandler</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>触发人工审核任务分发</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>FULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>TC_WF_RISK_PIPELINE</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>风控流程工作流</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>WORKFLOW</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>RISK</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>default-calendar</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>3600</v>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>事件触发完整风控流程</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>FULL</t>
         </is>
       </c>
     </row>
@@ -3654,55 +3650,55 @@
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>default-calendar</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>always-open</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>14400</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>GATEWAY joinMode=ALL 覆盖</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>FULL</t>
         </is>
       </c>
     </row>
@@ -3737,55 +3733,55 @@
           <t>MANUAL</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>default-calendar</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>always-open</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>14400</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>GATEWAY joinMode=N_OF + joinThreshold=2 覆盖</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>FULL</t>
         </is>
       </c>
     </row>

--- a/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/tc-tenant-config-package-test.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="resource_queue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="business_calendar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="batch_window" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="job_definition" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="file_channel_config" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="file_template_config" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="pipeline_definition" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="pipeline_step_definition" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="workflow_definition" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="workflow_node" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="workflow_edge" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resource_queue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="business_calendar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="batch_window" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="job_definition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_channel_config" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_template_config" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_definition" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_step_definition" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_definition" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_node" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_edge" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"templateCode":"TC_IMPORT_RISK_SCORE_TPL","content":"entity_id,entity_type,score_value,score_band,score_date\nWF-ENT-000001,ACCOUNT,701,MEDIUM,2026-06-08\n"}</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"templateCode":"TC_EXPORT_RISK_ALERT_TPL"}</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"jdbcMappedImport":{"schema":"biz","table":"risk_score","tenantColumn":"tenant_id","conflictColumns":["tenant_id","entity_id","score_date"],"columnMappings":[{"from":"entity_id","to":"entity_id"},{"from":"entity_type","to":"entity_type"},{"from":"score_value","to":"score_value","type":"INTEGER"},{"from":"score_band","to":"score_band"},{"from":"score_date","to":"score_date","type":"DATE","format":"yyyy-MM-dd"}]}}</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"export_data_ref":"sql_template_export","sqlTemplateExport":{"cursorColumn":"id"}}</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -5383,7 +5383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>接收加密文件</t>
+          <t>接收文件</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>解密预处理</t>
+          <t>预处理</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>解析JSON</t>
+          <t>解析</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"spec":"jdbcMappedImport","version":"1","commitBatchSize":500}</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>评分入库</t>
+          <t>入库</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"spec":"jdbcMappedImport","version":"1","commitBatchSize":500}</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
@@ -5673,6 +5673,60 @@
         <v>2</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TC_IMPORT_RISK_SCORE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>STEP_VALIDATE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>校验</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>VALIDATE</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>IMPORT_VALIDATE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>{"spec":"jdbcMappedImport","version":"1","commitBatchSize":500}</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
